--- a/job_application_forms/049_media_public_relations_manager_interview_form--job_application_forms.xlsx
+++ b/job_application_forms/049_media_public_relations_manager_interview_form--job_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>job_title_level</t>
+          <t>job_title_level_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Job Title Level</t>
+          <t>Job Title Level 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>years_of_service</t>
+          <t>years_of_service_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Years of Service</t>
+          <t>Years Of Service 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>job_status</t>
+          <t>job_status_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Job Status</t>
+          <t>Job Status 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -963,7 +963,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1039,7 +1039,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>job_title_level_choices</t>
+          <t>job_title_level_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1056,7 +1056,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>job_title_level_choices</t>
+          <t>job_title_level_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1073,7 +1073,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>job_title_level_choices</t>
+          <t>job_title_level_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1209,7 +1209,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1226,7 +1226,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1243,7 +1243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1260,7 +1260,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1277,7 +1277,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>job_status_choices</t>
+          <t>job_status_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
